--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2019_magallanes.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:01</t>
+    <t xml:space="preserve">2026-09-24 00:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -651,19 +651,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.24</v>
+        <v>-0.05</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>-0.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="9">
@@ -674,19 +674,19 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.17</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -697,19 +697,19 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +720,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="12">
@@ -766,19 +766,19 @@
         <v>22</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.44</v>
+        <v>0.13</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.07</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="14">
@@ -789,19 +789,19 @@
         <v>22</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.59</v>
+        <v>0.18</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.56</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -812,19 +812,19 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
